--- a/research/KNN EN.xlsx
+++ b/research/KNN EN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\04-Uniwersytet\01-Lectures\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B725817-AB3F-44A4-A996-AD2C03D77196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED6AF24-36D6-4846-9D2E-89D252B06E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lists" sheetId="6" r:id="rId1"/>
@@ -1262,7 +1262,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9A7BB60-4E66-4639-A489-F9C6AC99EE6D}" type="CELLRANGE">
+                    <a:fld id="{2E54932F-6B94-4714-B1BB-515C3BEE268A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1295,7 +1295,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A21D844F-051B-4557-B99D-E7B3B110EA5B}" type="CELLRANGE">
+                    <a:fld id="{86DAD28C-D60B-4604-ADE0-8DBCFF54FC57}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1329,7 +1329,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4CDBD120-BEB2-40D9-B435-D6C673468164}" type="CELLRANGE">
+                    <a:fld id="{91671317-9B29-45C7-90B6-656684DCEA29}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1363,7 +1363,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8881F259-B30A-4D35-B014-868411F14DCC}" type="CELLRANGE">
+                    <a:fld id="{B5E2ACF7-DD1A-4011-9BAD-0560A390A8FA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1397,7 +1397,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E557BD75-2D84-4850-A50B-E8B7F54C695C}" type="CELLRANGE">
+                    <a:fld id="{E29E1513-99A1-47DB-BB3C-22F8FFDF5F42}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1431,7 +1431,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9FAB16DE-90FD-44C3-BA11-27BD333480C8}" type="CELLRANGE">
+                    <a:fld id="{1FCF9843-2784-4F51-B9C7-DBC2425A3B5B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1465,7 +1465,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C5F79BD4-3821-497A-B87B-B02CFA772BCE}" type="CELLRANGE">
+                    <a:fld id="{37682E65-A59C-4766-B2D5-7BC0DA4F9E62}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1499,7 +1499,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7D1790AF-4448-4C72-88FA-0D37C96907B4}" type="CELLRANGE">
+                    <a:fld id="{F31ADD66-825F-4DAE-BB14-D9A58EF85586}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1533,7 +1533,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ABE91D09-FB63-4248-929D-A5029F8E818C}" type="CELLRANGE">
+                    <a:fld id="{51FC8BB1-D83D-4348-847F-0A452D3FF90D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1567,7 +1567,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B936D6E-E3D8-441E-B9AF-6545DCF7F057}" type="CELLRANGE">
+                    <a:fld id="{1C9ECC89-7D9C-4F35-B0BB-8196E51F6854}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1601,7 +1601,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{825A858D-F9E9-4997-971F-FC5C3FE795F7}" type="CELLRANGE">
+                    <a:fld id="{46A9D5F7-B451-48FF-B926-00BE66458892}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1635,7 +1635,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{077408C7-0991-4627-821E-278B6FC026FE}" type="CELLRANGE">
+                    <a:fld id="{A20A087E-E0DC-4C6F-9A0E-1C0A921DAC92}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1669,7 +1669,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2C706EBB-CD42-44FA-9D9F-61ADCB087F0B}" type="CELLRANGE">
+                    <a:fld id="{2F72A104-76A9-4574-BBA3-12E244ED8BF7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1703,7 +1703,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{15AA68FF-CB15-4461-921E-DD8B7FE5AEB8}" type="CELLRANGE">
+                    <a:fld id="{6C121108-9E68-43A1-BCF0-B3A739FF24FC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1737,7 +1737,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E736501B-1E5F-4C03-A514-08F9C875B47B}" type="CELLRANGE">
+                    <a:fld id="{BF19B025-D7B1-46AE-B266-FCDA55B15657}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2009,7 +2009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6809937A-3AD3-4590-93BE-C00D62685B08}" type="CELLRANGE">
+                    <a:fld id="{81AE8632-7C71-4FAD-8E93-BD2847E97EBF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2179,7 +2179,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL" sz="1200" b="1"/>
-                  <a:t>Długość</a:t>
+                  <a:t>Length</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2277,7 +2277,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL" sz="1200" b="1"/>
-                  <a:t>Szerokość</a:t>
+                  <a:t>Width</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2798,7 +2798,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FCA958CB-D8F3-46AF-AC44-6AFF7EB4DC81}" type="CELLRANGE">
+                    <a:fld id="{1E891B58-6C63-4455-B4ED-612BE65E4E9A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2831,7 +2831,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{85B76B4E-01BF-426D-B5DC-A4394B03BB9F}" type="CELLRANGE">
+                    <a:fld id="{AC64D798-3C50-4270-9C2B-E4AEE3442464}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2865,7 +2865,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D1CD168E-989D-4A89-A140-68D09653FB67}" type="CELLRANGE">
+                    <a:fld id="{A0DE9F93-557F-44DE-B565-E7104AA14CBF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2899,7 +2899,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C4DE28C4-A0D1-4284-8D6C-EE9BDCF6D905}" type="CELLRANGE">
+                    <a:fld id="{59280DE8-F0C8-4C67-856A-5FD167A1A5B0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2933,7 +2933,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0ACEE65C-6525-4335-89D1-9D9F0928733E}" type="CELLRANGE">
+                    <a:fld id="{7742C6DF-1819-4E07-82D6-DA5C2453C237}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2967,7 +2967,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7DD50E7B-5732-42F0-8F5F-8B13F384FC02}" type="CELLRANGE">
+                    <a:fld id="{5255BD59-38B4-4D2B-AD4B-11DB3BA1F59D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3001,7 +3001,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{80FF405D-6F74-4D85-AD5A-EF5DC604A8BD}" type="CELLRANGE">
+                    <a:fld id="{BA9987BA-D210-46D0-B862-80DA517C869B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3035,7 +3035,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{27A3AADB-25B0-4B11-A5D5-1598075D3981}" type="CELLRANGE">
+                    <a:fld id="{D5B47413-6543-4CFD-B07B-F617611AC143}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3069,7 +3069,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F44A8309-DC76-463C-BF1E-57A2BD2B1455}" type="CELLRANGE">
+                    <a:fld id="{80599A76-7FDB-425C-83CA-FF0CBEE4D7E8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3103,7 +3103,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{93D58823-F23D-4900-8726-DA23383899CB}" type="CELLRANGE">
+                    <a:fld id="{75A64442-DAEA-4A26-80A1-B02ED7844A27}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3137,7 +3137,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FA4F4B1B-5FFA-4240-9F6D-073B18869F13}" type="CELLRANGE">
+                    <a:fld id="{FEC660FF-AD12-411D-8AF1-CC08136F2188}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3171,7 +3171,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{69FF26CA-C10B-44FF-BAAF-8839E87CDAA8}" type="CELLRANGE">
+                    <a:fld id="{0FC5A0B6-2F11-47CB-A833-D4399F3CE319}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3205,7 +3205,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{08521D8E-7FA8-46DE-95B7-5957513460C5}" type="CELLRANGE">
+                    <a:fld id="{ED691498-1CBD-4A5A-BB64-88E8ED9B9A1C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3239,7 +3239,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{794282FB-F942-49C7-9508-BA084DF37DC7}" type="CELLRANGE">
+                    <a:fld id="{5D47C038-812A-40E9-B3DE-49048555594A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3273,7 +3273,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5BD964DB-882D-457D-BE74-BDC47E07F18D}" type="CELLRANGE">
+                    <a:fld id="{EDF96BB7-9295-41EF-A514-83BA70163AA8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3545,7 +3545,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AF66B97F-53D1-4913-9EBC-290E8B4A9631}" type="CELLRANGE">
+                    <a:fld id="{F68F64D9-01EA-48B6-9C00-67E1D3D768FE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>

--- a/research/KNN EN.xlsx
+++ b/research/KNN EN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\04-Uniwersytet\01-Lectures\Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\04-Uniwersytet\01-Lectures\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED6AF24-36D6-4846-9D2E-89D252B06E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FA8B4A-B835-4E82-A03C-AB2B439F7D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lists" sheetId="6" r:id="rId1"/>
@@ -1262,7 +1262,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2E54932F-6B94-4714-B1BB-515C3BEE268A}" type="CELLRANGE">
+                    <a:fld id="{4F5CD511-1CE9-453F-9FA5-462AE8379364}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1295,7 +1295,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{86DAD28C-D60B-4604-ADE0-8DBCFF54FC57}" type="CELLRANGE">
+                    <a:fld id="{45447FE8-ADEB-4C67-B050-01B38FA252A2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1329,7 +1329,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{91671317-9B29-45C7-90B6-656684DCEA29}" type="CELLRANGE">
+                    <a:fld id="{440E73DB-E329-41CF-8A64-4CEF02E5B775}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1363,7 +1363,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B5E2ACF7-DD1A-4011-9BAD-0560A390A8FA}" type="CELLRANGE">
+                    <a:fld id="{FB5C160B-F116-4BF8-941E-7762C3281C56}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1397,7 +1397,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E29E1513-99A1-47DB-BB3C-22F8FFDF5F42}" type="CELLRANGE">
+                    <a:fld id="{B7C7CEE5-F93E-4A92-82E1-9400161D0287}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1431,7 +1431,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1FCF9843-2784-4F51-B9C7-DBC2425A3B5B}" type="CELLRANGE">
+                    <a:fld id="{D0FDAEE3-FCC6-444D-B44F-EA4576C3B6B9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1465,7 +1465,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37682E65-A59C-4766-B2D5-7BC0DA4F9E62}" type="CELLRANGE">
+                    <a:fld id="{699F6C75-6487-4DBA-8ADB-6E8C879403BE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1499,7 +1499,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F31ADD66-825F-4DAE-BB14-D9A58EF85586}" type="CELLRANGE">
+                    <a:fld id="{C74A3B4A-A0B9-4056-89B2-62841B4DACC0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1533,7 +1533,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51FC8BB1-D83D-4348-847F-0A452D3FF90D}" type="CELLRANGE">
+                    <a:fld id="{159215D6-DA26-433D-AD5E-E4B38F7C1D8E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1567,7 +1567,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1C9ECC89-7D9C-4F35-B0BB-8196E51F6854}" type="CELLRANGE">
+                    <a:fld id="{FF2088FD-547F-428E-B011-0F59F582E7A7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1601,7 +1601,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{46A9D5F7-B451-48FF-B926-00BE66458892}" type="CELLRANGE">
+                    <a:fld id="{DA562F0D-F4CC-49B2-A061-A7419D35EF37}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1635,7 +1635,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A20A087E-E0DC-4C6F-9A0E-1C0A921DAC92}" type="CELLRANGE">
+                    <a:fld id="{AAC0660F-C120-4222-B318-A601857C0917}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1669,7 +1669,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F72A104-76A9-4574-BBA3-12E244ED8BF7}" type="CELLRANGE">
+                    <a:fld id="{79B26FE6-5097-4281-BBF1-B8B7E82F916F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1703,7 +1703,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6C121108-9E68-43A1-BCF0-B3A739FF24FC}" type="CELLRANGE">
+                    <a:fld id="{187E100F-C320-4E99-B0A6-C505BBB8DC8D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1737,7 +1737,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BF19B025-D7B1-46AE-B266-FCDA55B15657}" type="CELLRANGE">
+                    <a:fld id="{51E72C2E-138E-41BE-BEA9-F69D695DFBEF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2009,7 +2009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{81AE8632-7C71-4FAD-8E93-BD2847E97EBF}" type="CELLRANGE">
+                    <a:fld id="{EEAB3E80-75C3-496C-AF51-0A612168716C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2798,7 +2798,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1E891B58-6C63-4455-B4ED-612BE65E4E9A}" type="CELLRANGE">
+                    <a:fld id="{3BD0F79C-88A8-4E8A-90C9-DDB9436AC5CB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2831,7 +2831,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC64D798-3C50-4270-9C2B-E4AEE3442464}" type="CELLRANGE">
+                    <a:fld id="{33804A93-FD81-4EE7-BA0D-5A23C7B51E52}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2865,7 +2865,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A0DE9F93-557F-44DE-B565-E7104AA14CBF}" type="CELLRANGE">
+                    <a:fld id="{F1819E1F-06D0-426E-B323-53DF2828D194}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2899,7 +2899,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{59280DE8-F0C8-4C67-856A-5FD167A1A5B0}" type="CELLRANGE">
+                    <a:fld id="{2366F35A-6F22-4861-AC85-B5C2B54FD1D1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2933,7 +2933,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7742C6DF-1819-4E07-82D6-DA5C2453C237}" type="CELLRANGE">
+                    <a:fld id="{71C3371E-C0EF-4CC6-AD8E-E6E88321AE95}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2967,7 +2967,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5255BD59-38B4-4D2B-AD4B-11DB3BA1F59D}" type="CELLRANGE">
+                    <a:fld id="{7C602D19-4F16-4508-A9A4-FB0FDA8FF6CF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3001,7 +3001,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BA9987BA-D210-46D0-B862-80DA517C869B}" type="CELLRANGE">
+                    <a:fld id="{CD642795-D9B6-42A7-BCF4-0444679F0770}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3035,7 +3035,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D5B47413-6543-4CFD-B07B-F617611AC143}" type="CELLRANGE">
+                    <a:fld id="{E849AF75-DECA-4DD8-A8D7-595099A96D2E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3069,7 +3069,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{80599A76-7FDB-425C-83CA-FF0CBEE4D7E8}" type="CELLRANGE">
+                    <a:fld id="{5FDF7976-6AA3-48A5-ABDB-9FDD86B3DC7A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3103,7 +3103,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{75A64442-DAEA-4A26-80A1-B02ED7844A27}" type="CELLRANGE">
+                    <a:fld id="{6A328F9D-25DA-4B97-A6BF-07B7E4E599DD}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3137,7 +3137,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FEC660FF-AD12-411D-8AF1-CC08136F2188}" type="CELLRANGE">
+                    <a:fld id="{3F2A4E61-AA5C-4ABA-B9F0-D0C0B978029E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3171,7 +3171,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0FC5A0B6-2F11-47CB-A833-D4399F3CE319}" type="CELLRANGE">
+                    <a:fld id="{7A48086C-E434-433A-BF98-97A8F06F0E29}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3205,7 +3205,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ED691498-1CBD-4A5A-BB64-88E8ED9B9A1C}" type="CELLRANGE">
+                    <a:fld id="{4C0B8A85-1BDC-4E66-B219-12C09E55111E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3239,7 +3239,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5D47C038-812A-40E9-B3DE-49048555594A}" type="CELLRANGE">
+                    <a:fld id="{737AC039-03D7-4ADD-8AE6-4F56187F75AE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3273,7 +3273,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EDF96BB7-9295-41EF-A514-83BA70163AA8}" type="CELLRANGE">
+                    <a:fld id="{279BC7D4-257D-4F70-A0FB-5527A96DE588}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3545,7 +3545,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F68F64D9-01EA-48B6-9C00-67E1D3D768FE}" type="CELLRANGE">
+                    <a:fld id="{BD2310E7-EA19-4BE9-85F1-44BC1D56E89F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -4192,20 +4192,20 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:Q200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.6328125" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" style="8"/>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="8"/>
     <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6328125" customWidth="1"/>
-    <col min="13" max="13" width="15.26953125" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>6</v>
       </c>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>8</v>
       </c>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>9</v>
       </c>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>11</v>
       </c>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>Q</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>R</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>T</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>U</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>V</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>W</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>X</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>Z</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>AA</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>AB</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>AC</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>AD</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>AE</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>AF</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>AG</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>AH</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>AI</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>AJ</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>AK</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>AL</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>AM</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>AN</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>AO</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>AP</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>AQ</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>AR</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>AS</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>AT</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>AU</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>AV</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>AW</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>AX</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>AY</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>AZ</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>BA</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>BB</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>BC</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>BD</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>BE</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>BF</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>BG</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>BH</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>59</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>BI</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>60</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>BJ</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>BK</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>BL</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>BM</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>BN</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>BO</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>BP</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>BQ</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>BR</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>BS</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>BT</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>BU</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>BV</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>BW</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>BX</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>BY</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -5279,7 +5279,7 @@
         <v>BZ</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>77</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>78</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>CB</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>79</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>CC</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>80</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>CD</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>81</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>CE</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>82</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>CF</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>83</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>CG</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>84</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>CH</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>85</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>CI</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>86</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>CJ</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>87</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>CK</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>88</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>CL</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>89</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>CM</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>90</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>CN</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>91</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>CO</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>92</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>CP</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>93</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>CQ</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>94</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>CR</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>95</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>CS</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>96</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>CT</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>97</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>CU</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>98</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>CV</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>99</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>CW</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>100</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>CX</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>101</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>CY</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>102</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>CZ</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>103</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>DA</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>104</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>DB</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>105</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>DC</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>106</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>DD</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>107</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>DE</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>108</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>DF</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>109</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>DG</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>110</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>DH</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>111</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>DI</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>112</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>DJ</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>113</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>DK</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>114</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>DL</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>115</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>DM</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>116</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>DN</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>117</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>DO</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>118</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>DP</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>119</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>DQ</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>120</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>DR</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>121</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>DS</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>122</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>DT</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>123</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>DU</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>124</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>DV</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>125</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>DW</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>126</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>DX</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>127</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>DY</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>128</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>DZ</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>129</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>EA</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>130</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>EB</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>131</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>EC</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>132</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>ED</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>133</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>EE</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>134</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>EF</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>135</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>EG</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>136</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>EH</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>137</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>EI</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>138</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>EJ</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>139</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>EK</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>140</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>EL</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>141</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>EM</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>142</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>EN</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>143</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>EO</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>144</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>EP</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>145</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>EQ</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>146</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>ER</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>147</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>ES</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>148</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>ET</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>149</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>EU</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>150</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>EV</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>151</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>EW</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>152</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>EX</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>153</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>EY</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>154</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>EZ</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>155</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>FA</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>156</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>FB</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>157</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>FC</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>158</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>FD</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>159</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>FE</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>160</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>FF</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>161</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>FG</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>162</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>FH</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>163</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>FI</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>164</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>FJ</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>165</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>FK</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>166</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>FL</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>167</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>FM</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>168</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>FN</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>169</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>FO</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>170</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>FP</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>171</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>FQ</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>172</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>FR</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>173</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>FS</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>174</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>FT</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>175</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>FU</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>176</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>FV</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>177</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>FW</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>178</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>FX</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>179</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>FY</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>180</v>
       </c>
@@ -6215,7 +6215,7 @@
         <v>FZ</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>181</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>GA</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>182</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>GB</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>183</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>GC</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>184</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>GD</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>185</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>GE</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>186</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>GF</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>187</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>GG</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>188</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>GH</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>189</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>GI</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>190</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>GJ</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>191</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>GK</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>192</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>GL</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>193</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>GM</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>194</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>GN</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>195</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>GO</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>196</v>
       </c>
@@ -6359,7 +6359,7 @@
         <v>GP</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>197</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>GQ</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>198</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>GR</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>199</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>GS</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>200</v>
       </c>
@@ -6434,24 +6434,24 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>Z</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>Z</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I16" s="41"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -7004,10 +7004,10 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25" s="5"/>
     </row>
   </sheetData>
@@ -7079,31 +7079,31 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AM19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.6328125" customWidth="1"/>
-    <col min="4" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" customWidth="1"/>
-    <col min="10" max="10" width="10.90625" customWidth="1"/>
-    <col min="12" max="12" width="8.453125" customWidth="1"/>
-    <col min="13" max="13" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
-    <col min="17" max="17" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="7.453125" customWidth="1"/>
-    <col min="20" max="20" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="7.453125" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="7.44140625" customWidth="1"/>
+    <col min="20" max="20" width="11.88671875" customWidth="1"/>
+    <col min="21" max="24" width="7.44140625" customWidth="1"/>
     <col min="25" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.1796875" customWidth="1"/>
-    <col min="29" max="29" width="11.90625" customWidth="1"/>
-    <col min="34" max="35" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.90625" customWidth="1"/>
-    <col min="39" max="39" width="9.81640625" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.21875" customWidth="1"/>
+    <col min="29" max="29" width="11.88671875" customWidth="1"/>
+    <col min="34" max="35" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.88671875" customWidth="1"/>
+    <col min="39" max="39" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
@@ -7117,7 +7117,7 @@
       <c r="AH1" s="48"/>
       <c r="AI1" s="49"/>
     </row>
-    <row r="2" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="40" t="s">
         <v>28</v>
       </c>
@@ -7154,7 +7154,7 @@
       <c r="AL2" s="51"/>
       <c r="AM2" s="52"/>
     </row>
-    <row r="3" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:39" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -7600,7 +7600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>7</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>8</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>9</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>10</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>11</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>12</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>13</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
         <v>14</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <v>15</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>16</v>
       </c>
